--- a/data/k-props/2026-08-02.xlsx
+++ b/data/k-props/2026-08-02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="101">
   <si>
     <t>date</t>
   </si>
@@ -145,51 +145,45 @@
     <t>2026-08-02</t>
   </si>
   <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Cade Cavalli</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Atlanta Braves</t>
+  </si>
+  <si>
     <t>JR Ritchie</t>
   </si>
   <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
-    <t>Cade Cavalli</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Baltimore Orioles</t>
-  </si>
-  <si>
     <t>Matthew Liberatore</t>
   </si>
   <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>St. Louis Cardinals @ Toronto Blue Jays</t>
   </si>
   <si>
@@ -205,45 +199,54 @@
     <t>Arizona Diamondbacks @ Cleveland Guardians</t>
   </si>
   <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Mitch Keller</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>Anthony Kay</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Tampa Bay Rays</t>
+  </si>
+  <si>
     <t>Griffin Jax</t>
   </si>
   <si>
-    <t>Chicago White Sox @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
+    <t>Sandy Alcantara</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ New York Mets</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Gerrit Cole</t>
   </si>
   <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Pittsburgh Pirates @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Sandy Alcantara</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ New York Mets</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Peter Lambert</t>
+    <t>New York Yankees @ Chicago Cubs</t>
   </si>
   <si>
     <t>Colin Rea</t>
   </si>
   <si>
-    <t>New York Yankees @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Gerrit Cole</t>
-  </si>
-  <si>
     <t>Seth Lugo</t>
   </si>
   <si>
@@ -259,70 +262,58 @@
     <t>Milwaukee Brewers @ Los Angeles Angels</t>
   </si>
   <si>
+    <t>Walbert Ureña</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Athletics</t>
+  </si>
+  <si>
+    <t>Gage Jump</t>
+  </si>
+  <si>
+    <t>Landen Roupp</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Kyle Hart</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Taj Bradley</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Emmet Sheehan</t>
+  </si>
+  <si>
     <t>Walbert Urena</t>
   </si>
   <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Athletics</t>
-  </si>
-  <si>
-    <t>Gage Jump</t>
-  </si>
-  <si>
-    <t>George Kirby</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Taj Bradley</t>
-  </si>
-  <si>
-    <t>Landen Roupp</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Los Angeles Dodgers</t>
+    <t>Robert Stock</t>
+  </si>
+  <si>
+    <t>Michael King</t>
   </si>
   <si>
     <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Emmet Sheehan</t>
-  </si>
-  <si>
-    <t>Kyle Bradish</t>
-  </si>
-  <si>
-    <t>Gavin Williams</t>
-  </si>
-  <si>
-    <t>Mitch Keller</t>
-  </si>
-  <si>
-    <t>Anthony Kay</t>
-  </si>
-  <si>
-    <t>Walbert Ureña</t>
-  </si>
-  <si>
-    <t>Kyle Hart</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Robert Stock</t>
-  </si>
-  <si>
-    <t>Michael King</t>
   </si>
 </sst>
 </file>
@@ -848,46 +839,40 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D2">
-        <v>-110</v>
+        <v>-160</v>
       </c>
       <c r="E2">
-        <v>-120</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>4.08</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>7.51</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
       </c>
-      <c r="I2">
-        <v>-1.42</v>
-      </c>
       <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2">
+        <v>7.51</v>
+      </c>
+      <c r="L2" t="s">
         <v>46</v>
       </c>
-      <c r="K2">
-        <v>4.08</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>47</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2">
+        <v>824807</v>
+      </c>
+      <c r="O2" t="s">
         <v>48</v>
       </c>
-      <c r="N2">
-        <v>824891</v>
-      </c>
-      <c r="O2" t="s">
-        <v>49</v>
-      </c>
       <c r="P2">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -898,41 +883,65 @@
       <c r="S2">
         <v>2</v>
       </c>
+      <c r="T2">
+        <v>0.3063</v>
+      </c>
+      <c r="U2">
+        <v>0.3196</v>
+      </c>
+      <c r="V2">
+        <v>5</v>
+      </c>
+      <c r="W2">
+        <v>98</v>
+      </c>
+      <c r="X2">
+        <v>0.3469</v>
+      </c>
+      <c r="Y2">
+        <v>0.329</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
       <c r="AA2">
-        <v>4.38</v>
+        <v>3.91</v>
+      </c>
+      <c r="AB2">
+        <v>1.0352</v>
       </c>
       <c r="AC2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD2">
+        <v>0.2239</v>
+      </c>
+      <c r="AE2">
+        <v>0.2234</v>
+      </c>
+      <c r="AF2">
+        <v>9</v>
+      </c>
+      <c r="AG2">
+        <v>0.2383</v>
+      </c>
+      <c r="AH2">
+        <v>0.2163</v>
       </c>
       <c r="AI2">
-        <v>1.0222</v>
+        <v>1.0001</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
       </c>
       <c r="AK2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>-0.08</v>
-      </c>
-      <c r="AO2">
-        <v>0.08</v>
-      </c>
-      <c r="AP2">
-        <v>-0.08</v>
-      </c>
-      <c r="AQ2">
-        <v>0.08</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
@@ -940,94 +949,103 @@
         <v>43</v>
       </c>
       <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3">
+        <v>5.52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3">
+        <v>5.36</v>
+      </c>
+      <c r="L3" t="s">
         <v>52</v>
       </c>
-      <c r="C3">
+      <c r="M3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3">
+        <v>824807</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3">
         <v>5.5</v>
       </c>
-      <c r="D3">
-        <v>-105</v>
-      </c>
-      <c r="E3">
-        <v>-125</v>
-      </c>
-      <c r="F3">
-        <v>5.21</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3">
-        <v>-0.29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3">
-        <v>5.21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3">
-        <v>824891</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0.2262</v>
+      </c>
+      <c r="U3">
+        <v>0.2132</v>
+      </c>
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>106</v>
+      </c>
+      <c r="X3">
+        <v>0.1887</v>
+      </c>
+      <c r="Y3">
+        <v>0.346</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>4.21</v>
+      </c>
+      <c r="AB3">
+        <v>1.0992</v>
+      </c>
+      <c r="AC3" t="s">
         <v>49</v>
       </c>
-      <c r="P3">
-        <v>4.9</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="AA3">
-        <v>4.3</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>50</v>
+      <c r="AD3">
+        <v>0.2378</v>
+      </c>
+      <c r="AE3">
+        <v>0.2409</v>
+      </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
+      <c r="AG3">
+        <v>0.2267</v>
+      </c>
+      <c r="AH3">
+        <v>0.2163</v>
       </c>
       <c r="AI3">
-        <v>0.9801</v>
+        <v>0.9839</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
       </c>
       <c r="AK3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>-2.21</v>
-      </c>
-      <c r="AO3">
-        <v>2.21</v>
-      </c>
-      <c r="AP3">
-        <v>-2.21</v>
-      </c>
-      <c r="AQ3">
-        <v>2.21</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
@@ -1038,91 +1056,109 @@
         <v>53</v>
       </c>
       <c r="C4">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D4">
-        <v>-160</v>
+        <v>-105</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>-125</v>
       </c>
       <c r="F4">
-        <v>6.06</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
       </c>
-      <c r="I4">
-        <v>-1.44</v>
-      </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4">
-        <v>7.44</v>
+        <v>5.74</v>
       </c>
       <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
         <v>54</v>
       </c>
-      <c r="M4" t="s">
-        <v>55</v>
-      </c>
       <c r="N4">
-        <v>824807</v>
+        <v>824891</v>
       </c>
       <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4">
+        <v>5.1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0.2554</v>
+      </c>
+      <c r="U4">
+        <v>0.2573</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>119</v>
+      </c>
+      <c r="X4">
+        <v>0.2605</v>
+      </c>
+      <c r="Y4">
+        <v>0.373</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>4.29</v>
+      </c>
+      <c r="AB4">
+        <v>1.0305</v>
+      </c>
+      <c r="AC4" t="s">
         <v>49</v>
       </c>
-      <c r="P4">
-        <v>5.8</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>2</v>
-      </c>
-      <c r="AA4">
-        <v>3.85</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>50</v>
+      <c r="AD4">
+        <v>0.2229</v>
+      </c>
+      <c r="AE4">
+        <v>0.2176</v>
+      </c>
+      <c r="AF4">
+        <v>9</v>
+      </c>
+      <c r="AG4">
+        <v>0.2179</v>
+      </c>
+      <c r="AH4">
+        <v>0.2163</v>
       </c>
       <c r="AI4">
-        <v>0.9931</v>
+        <v>0.9802</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>-1.38</v>
-      </c>
-      <c r="AN4">
-        <v>-4.44</v>
-      </c>
-      <c r="AO4">
-        <v>4.44</v>
-      </c>
-      <c r="AP4">
-        <v>-3.06</v>
-      </c>
-      <c r="AQ4">
-        <v>3.06</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
@@ -1130,49 +1166,43 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>130</v>
+        <v>-110</v>
       </c>
       <c r="E5">
-        <v>-135</v>
+        <v>-120</v>
       </c>
       <c r="F5">
-        <v>4.01</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
+        <v>4.14</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5">
-        <v>-2.49</v>
+        <v>45</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K5">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N5">
-        <v>822783</v>
+        <v>824891</v>
       </c>
       <c r="O5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1183,41 +1213,65 @@
       <c r="S5">
         <v>2</v>
       </c>
+      <c r="T5">
+        <v>0.207</v>
+      </c>
+      <c r="U5">
+        <v>0.2112</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <v>105</v>
+      </c>
+      <c r="X5">
+        <v>0.219</v>
+      </c>
+      <c r="Y5">
+        <v>0.344</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
       <c r="AA5">
-        <v>4.43</v>
+        <v>4.41</v>
+      </c>
+      <c r="AB5">
+        <v>0.8433</v>
       </c>
       <c r="AC5" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD5">
+        <v>0.1824</v>
+      </c>
+      <c r="AE5">
+        <v>0.192</v>
+      </c>
+      <c r="AF5">
+        <v>9</v>
+      </c>
+      <c r="AG5">
+        <v>0.2059</v>
+      </c>
+      <c r="AH5">
+        <v>0.2163</v>
       </c>
       <c r="AI5">
-        <v>0.9118</v>
+        <v>1.021</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>2.99</v>
-      </c>
-      <c r="AO5">
-        <v>2.99</v>
-      </c>
-      <c r="AP5">
-        <v>2.99</v>
-      </c>
-      <c r="AQ5">
-        <v>2.99</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
@@ -1225,49 +1279,43 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D6">
-        <v>-120</v>
+        <v>130</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>-135</v>
       </c>
       <c r="F6">
-        <v>2.15</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
+        <v>3.21</v>
       </c>
       <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6">
+        <v>3.05</v>
+      </c>
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" t="s">
         <v>57</v>
-      </c>
-      <c r="I6">
-        <v>-2.35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6">
-        <v>2.15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" t="s">
-        <v>59</v>
       </c>
       <c r="N6">
         <v>822783</v>
       </c>
       <c r="O6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1278,41 +1326,65 @@
       <c r="S6">
         <v>2</v>
       </c>
+      <c r="T6">
+        <v>0.22</v>
+      </c>
+      <c r="U6">
+        <v>0.2323</v>
+      </c>
+      <c r="V6">
+        <v>5</v>
+      </c>
+      <c r="W6">
+        <v>110</v>
+      </c>
+      <c r="X6">
+        <v>0.2545</v>
+      </c>
+      <c r="Y6">
+        <v>0.355</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
       <c r="AA6">
-        <v>4.61</v>
+        <v>4.4</v>
+      </c>
+      <c r="AB6">
+        <v>0.6578</v>
       </c>
       <c r="AC6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD6">
+        <v>0.1423</v>
+      </c>
+      <c r="AE6">
+        <v>0.1457</v>
+      </c>
+      <c r="AF6">
+        <v>9</v>
+      </c>
+      <c r="AG6">
+        <v>0.2164</v>
+      </c>
+      <c r="AH6">
+        <v>0.2163</v>
       </c>
       <c r="AI6">
-        <v>0.8856</v>
+        <v>0.9177</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>2.85</v>
-      </c>
-      <c r="AO6">
-        <v>2.85</v>
-      </c>
-      <c r="AP6">
-        <v>2.85</v>
-      </c>
-      <c r="AQ6">
-        <v>2.85</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1320,49 +1392,43 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D7">
-        <v>115</v>
+        <v>-120</v>
       </c>
       <c r="E7">
-        <v>-150</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>3.14</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7">
+        <v>2.44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" t="s">
         <v>57</v>
       </c>
-      <c r="I7">
-        <v>-0.36</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7">
-        <v>3.14</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" t="s">
-        <v>63</v>
-      </c>
       <c r="N7">
-        <v>824404</v>
+        <v>822783</v>
       </c>
       <c r="O7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="P7">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1373,41 +1439,65 @@
       <c r="S7">
         <v>2</v>
       </c>
+      <c r="T7">
+        <v>0.1677</v>
+      </c>
+      <c r="U7">
+        <v>0.1725</v>
+      </c>
+      <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>93</v>
+      </c>
+      <c r="X7">
+        <v>0.1828</v>
+      </c>
+      <c r="Y7">
+        <v>0.317</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
       <c r="AA7">
-        <v>4.31</v>
+        <v>4.47</v>
+      </c>
+      <c r="AB7">
+        <v>0.8973</v>
       </c>
       <c r="AC7" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD7">
+        <v>0.1941</v>
+      </c>
+      <c r="AE7">
+        <v>0.1946</v>
+      </c>
+      <c r="AF7">
+        <v>9</v>
+      </c>
+      <c r="AG7">
+        <v>0.2126</v>
+      </c>
+      <c r="AH7">
+        <v>0.2163</v>
       </c>
       <c r="AI7">
-        <v>0.8907</v>
+        <v>0.88</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1.86</v>
-      </c>
-      <c r="AO7">
-        <v>1.86</v>
-      </c>
-      <c r="AP7">
-        <v>1.86</v>
-      </c>
-      <c r="AQ7">
-        <v>1.86</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
@@ -1415,49 +1505,43 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E8">
-        <v>-155</v>
+        <v>-150</v>
       </c>
       <c r="F8">
-        <v>5.03</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
+        <v>3.57</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8">
-        <v>-1.47</v>
+        <v>45</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K8">
-        <v>5.03</v>
+        <v>3.41</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N8">
-        <v>822943</v>
+        <v>824404</v>
       </c>
       <c r="O8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1468,41 +1552,65 @@
       <c r="S8">
         <v>2</v>
       </c>
+      <c r="T8">
+        <v>0.1541</v>
+      </c>
+      <c r="U8">
+        <v>0.1683</v>
+      </c>
+      <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>108</v>
+      </c>
+      <c r="X8">
+        <v>0.1944</v>
+      </c>
+      <c r="Y8">
+        <v>0.351</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
       <c r="AA8">
-        <v>4.15</v>
+        <v>4.33</v>
+      </c>
+      <c r="AB8">
+        <v>0.9231</v>
       </c>
       <c r="AC8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD8">
+        <v>0.1997</v>
+      </c>
+      <c r="AE8">
+        <v>0.2011</v>
+      </c>
+      <c r="AF8">
+        <v>9</v>
+      </c>
+      <c r="AG8">
+        <v>0.2176</v>
+      </c>
+      <c r="AH8">
+        <v>0.2163</v>
       </c>
       <c r="AI8">
-        <v>1.0074</v>
+        <v>0.8884</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>2.97</v>
-      </c>
-      <c r="AO8">
-        <v>2.97</v>
-      </c>
-      <c r="AP8">
-        <v>2.97</v>
-      </c>
-      <c r="AQ8">
-        <v>2.97</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
@@ -1510,94 +1618,103 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-      <c r="D9">
-        <v>-130</v>
-      </c>
-      <c r="E9">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>6.47</v>
-      </c>
-      <c r="G9">
+        <v>6.05</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9">
+        <v>5.89</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9">
+        <v>824404</v>
+      </c>
+      <c r="O9" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0.3229</v>
+      </c>
+      <c r="U9">
+        <v>0.3692</v>
+      </c>
+      <c r="V9">
+        <v>5</v>
+      </c>
+      <c r="W9">
+        <v>113</v>
+      </c>
+      <c r="X9">
+        <v>0.4513</v>
+      </c>
+      <c r="Y9">
+        <v>0.361</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>3.96</v>
+      </c>
+      <c r="AB9">
+        <v>0.7593</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD9">
+        <v>0.1642</v>
+      </c>
+      <c r="AE9">
+        <v>0.1694</v>
+      </c>
+      <c r="AF9">
         <v>9</v>
       </c>
-      <c r="H9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9">
-        <v>0.97</v>
-      </c>
-      <c r="J9" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9">
-        <v>6.63</v>
-      </c>
-      <c r="L9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" t="s">
-        <v>68</v>
-      </c>
-      <c r="N9">
-        <v>824483</v>
-      </c>
-      <c r="O9" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9">
-        <v>5.4</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>2</v>
-      </c>
-      <c r="AA9">
-        <v>4.03</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>50</v>
+      <c r="AG9">
+        <v>0.2003</v>
+      </c>
+      <c r="AH9">
+        <v>0.2163</v>
       </c>
       <c r="AI9">
-        <v>1.0203</v>
+        <v>0.88</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>-0.16</v>
-      </c>
-      <c r="AN9">
-        <v>2.37</v>
-      </c>
-      <c r="AO9">
-        <v>2.37</v>
-      </c>
-      <c r="AP9">
-        <v>2.53</v>
-      </c>
-      <c r="AQ9">
-        <v>2.53</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
@@ -1605,94 +1722,103 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10">
-        <v>5.5</v>
-      </c>
-      <c r="D10">
-        <v>105</v>
-      </c>
-      <c r="E10">
-        <v>-125</v>
+        <v>63</v>
       </c>
       <c r="F10">
-        <v>4.69</v>
-      </c>
-      <c r="G10">
+        <v>5.24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10">
+        <v>5.08</v>
+      </c>
+      <c r="L10" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10">
+        <v>824483</v>
+      </c>
+      <c r="O10" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10">
+        <v>5.3</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0.1769</v>
+      </c>
+      <c r="U10">
+        <v>0.1707</v>
+      </c>
+      <c r="V10">
         <v>5</v>
       </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10">
-        <v>-0.81</v>
-      </c>
-      <c r="J10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10">
-        <v>4.69</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="s">
-        <v>70</v>
-      </c>
-      <c r="N10">
-        <v>823592</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="W10">
+        <v>101</v>
+      </c>
+      <c r="X10">
+        <v>0.1584</v>
+      </c>
+      <c r="Y10">
+        <v>0.336</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>4.35</v>
+      </c>
+      <c r="AB10">
+        <v>1.2576</v>
+      </c>
+      <c r="AC10" t="s">
         <v>49</v>
       </c>
-      <c r="P10">
-        <v>6.3</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>2</v>
-      </c>
-      <c r="AA10">
-        <v>4.14</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>50</v>
+      <c r="AD10">
+        <v>0.272</v>
+      </c>
+      <c r="AE10">
+        <v>0.252</v>
+      </c>
+      <c r="AF10">
+        <v>9</v>
+      </c>
+      <c r="AG10">
+        <v>0.2549</v>
+      </c>
+      <c r="AH10">
+        <v>0.2163</v>
       </c>
       <c r="AI10">
-        <v>0.9517</v>
+        <v>1.0351</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0.31</v>
-      </c>
-      <c r="AO10">
-        <v>0.31</v>
-      </c>
-      <c r="AP10">
-        <v>0.31</v>
-      </c>
-      <c r="AQ10">
-        <v>0.31</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
@@ -1700,94 +1826,112 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>-120</v>
+        <v>-130</v>
       </c>
       <c r="E11">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11">
-        <v>4.32</v>
-      </c>
-      <c r="G11">
+        <v>7.21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>7.21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11">
+        <v>824483</v>
+      </c>
+      <c r="O11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11">
+        <v>5.6</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>0.2849</v>
+      </c>
+      <c r="U11">
+        <v>0.2691</v>
+      </c>
+      <c r="V11">
         <v>5</v>
       </c>
-      <c r="H11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11">
-        <v>-0.18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11">
-        <v>4.32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11">
-        <v>824163</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="W11">
+        <v>112</v>
+      </c>
+      <c r="X11">
+        <v>0.2411</v>
+      </c>
+      <c r="Y11">
+        <v>0.359</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>4.05</v>
+      </c>
+      <c r="AB11">
+        <v>1.1316</v>
+      </c>
+      <c r="AC11" t="s">
         <v>49</v>
       </c>
-      <c r="P11">
-        <v>5</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>6</v>
-      </c>
-      <c r="AA11">
-        <v>4.25</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>50</v>
+      <c r="AD11">
+        <v>0.2448</v>
+      </c>
+      <c r="AE11">
+        <v>0.2408</v>
+      </c>
+      <c r="AF11">
+        <v>8</v>
+      </c>
+      <c r="AG11">
+        <v>0.2359</v>
+      </c>
+      <c r="AH11">
+        <v>0.2163</v>
       </c>
       <c r="AI11">
-        <v>0.9557</v>
+        <v>1.0382</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0.68</v>
-      </c>
-      <c r="AO11">
-        <v>0.68</v>
-      </c>
-      <c r="AP11">
-        <v>0.68</v>
-      </c>
-      <c r="AQ11">
-        <v>0.68</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
@@ -1795,94 +1939,103 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-      <c r="D12">
-        <v>-110</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>5.9</v>
-      </c>
-      <c r="G12">
-        <v>8</v>
+        <v>3.59</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12">
-        <v>0.4</v>
+        <v>45</v>
       </c>
       <c r="J12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K12">
-        <v>6.06</v>
+        <v>3.43</v>
       </c>
       <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" t="s">
         <v>67</v>
       </c>
-      <c r="M12" t="s">
-        <v>72</v>
-      </c>
       <c r="N12">
-        <v>824163</v>
+        <v>822943</v>
       </c>
       <c r="O12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0.1811</v>
+      </c>
+      <c r="U12">
+        <v>0.1874</v>
+      </c>
+      <c r="V12">
+        <v>5</v>
+      </c>
+      <c r="W12">
+        <v>116</v>
+      </c>
+      <c r="X12">
+        <v>0.1983</v>
+      </c>
+      <c r="Y12">
+        <v>0.367</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>4.47</v>
+      </c>
+      <c r="AB12">
+        <v>0.9388</v>
+      </c>
+      <c r="AC12" t="s">
         <v>49</v>
       </c>
-      <c r="P12">
-        <v>5.7</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>6</v>
-      </c>
-      <c r="AA12">
-        <v>4.17</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>50</v>
+      <c r="AD12">
+        <v>0.2031</v>
+      </c>
+      <c r="AE12">
+        <v>0.2</v>
+      </c>
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>0.183</v>
+      </c>
+      <c r="AH12">
+        <v>0.2163</v>
       </c>
       <c r="AI12">
-        <v>1.0992</v>
+        <v>0.88</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM12">
-        <v>-0.16</v>
-      </c>
-      <c r="AN12">
-        <v>1.94</v>
-      </c>
-      <c r="AO12">
-        <v>1.94</v>
-      </c>
-      <c r="AP12">
-        <v>2.1</v>
-      </c>
-      <c r="AQ12">
-        <v>2.1</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
@@ -1890,94 +2043,112 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-143</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>124</v>
+        <v>-155</v>
       </c>
       <c r="F13">
-        <v>4.47</v>
-      </c>
-      <c r="G13">
-        <v>7</v>
+        <v>7.32</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13">
-        <v>-0.03</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K13">
-        <v>4.47</v>
+        <v>7.32</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N13">
-        <v>824648</v>
+        <v>822943</v>
       </c>
       <c r="O13" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13">
+        <v>4.6</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <v>0.2639</v>
+      </c>
+      <c r="U13">
+        <v>0.2708</v>
+      </c>
+      <c r="V13">
+        <v>5</v>
+      </c>
+      <c r="W13">
+        <v>113</v>
+      </c>
+      <c r="X13">
+        <v>0.2832</v>
+      </c>
+      <c r="Y13">
+        <v>0.361</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>4.13</v>
+      </c>
+      <c r="AB13">
+        <v>1.3953</v>
+      </c>
+      <c r="AC13" t="s">
         <v>49</v>
       </c>
-      <c r="P13">
-        <v>5.3</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>6</v>
-      </c>
-      <c r="AA13">
-        <v>4.35</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>50</v>
+      <c r="AD13">
+        <v>0.3018</v>
+      </c>
+      <c r="AE13">
+        <v>0.2368</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>0.2371</v>
+      </c>
+      <c r="AH13">
+        <v>0.2163</v>
       </c>
       <c r="AI13">
-        <v>1.038</v>
+        <v>1.02</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>2.53</v>
-      </c>
-      <c r="AO13">
-        <v>2.53</v>
-      </c>
-      <c r="AP13">
-        <v>2.53</v>
-      </c>
-      <c r="AQ13">
-        <v>2.53</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -1985,94 +2156,112 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C14">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
         <v>105</v>
       </c>
       <c r="E14">
-        <v>-121</v>
+        <v>-125</v>
       </c>
       <c r="F14">
-        <v>5.77</v>
-      </c>
-      <c r="G14">
+        <v>6.15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14">
+        <v>5.99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N14">
+        <v>823592</v>
+      </c>
+      <c r="O14" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14">
+        <v>6.5</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>0.1899</v>
+      </c>
+      <c r="U14">
+        <v>0.1993</v>
+      </c>
+      <c r="V14">
         <v>5</v>
       </c>
-      <c r="H14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14">
-        <v>-0.73</v>
-      </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14">
-        <v>5.77</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M14" t="s">
-        <v>75</v>
-      </c>
-      <c r="N14">
-        <v>824648</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="W14">
+        <v>131</v>
+      </c>
+      <c r="X14">
+        <v>0.2137</v>
+      </c>
+      <c r="Y14">
+        <v>0.396</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>4.12</v>
+      </c>
+      <c r="AB14">
+        <v>1.1641</v>
+      </c>
+      <c r="AC14" t="s">
         <v>49</v>
       </c>
-      <c r="P14">
-        <v>5.7</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>6</v>
-      </c>
-      <c r="AA14">
-        <v>4.1</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>50</v>
+      <c r="AD14">
+        <v>0.2518</v>
+      </c>
+      <c r="AE14">
+        <v>0.2338</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>0.2241</v>
+      </c>
+      <c r="AH14">
+        <v>0.2163</v>
       </c>
       <c r="AI14">
-        <v>0.9592</v>
+        <v>0.9568</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>-0.77</v>
-      </c>
-      <c r="AO14">
-        <v>0.77</v>
-      </c>
-      <c r="AP14">
-        <v>-0.77</v>
-      </c>
-      <c r="AQ14">
-        <v>0.77</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
@@ -2080,49 +2269,43 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>126</v>
+        <v>-120</v>
       </c>
       <c r="E15">
-        <v>-157</v>
+        <v>106</v>
       </c>
       <c r="F15">
-        <v>4.28</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
+        <v>4.71</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
       </c>
-      <c r="I15">
-        <v>-0.22</v>
-      </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K15">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N15">
-        <v>824323</v>
+        <v>824163</v>
       </c>
       <c r="O15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P15">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2133,41 +2316,65 @@
       <c r="S15">
         <v>6</v>
       </c>
+      <c r="T15">
+        <v>0.2141</v>
+      </c>
+      <c r="U15">
+        <v>0.2252</v>
+      </c>
+      <c r="V15">
+        <v>5</v>
+      </c>
+      <c r="W15">
+        <v>119</v>
+      </c>
+      <c r="X15">
+        <v>0.2437</v>
+      </c>
+      <c r="Y15">
+        <v>0.373</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
       <c r="AA15">
-        <v>4.23</v>
+        <v>4.33</v>
+      </c>
+      <c r="AB15">
+        <v>0.9995</v>
       </c>
       <c r="AC15" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD15">
+        <v>0.2162</v>
+      </c>
+      <c r="AE15">
+        <v>0.2073</v>
+      </c>
+      <c r="AF15">
+        <v>9</v>
+      </c>
+      <c r="AG15">
+        <v>0.2164</v>
+      </c>
+      <c r="AH15">
+        <v>0.2163</v>
       </c>
       <c r="AI15">
-        <v>0.9831</v>
+        <v>0.949</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>-1.28</v>
-      </c>
-      <c r="AO15">
-        <v>1.28</v>
-      </c>
-      <c r="AP15">
-        <v>-1.28</v>
-      </c>
-      <c r="AQ15">
-        <v>1.28</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
@@ -2175,49 +2382,43 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D16">
-        <v>130</v>
+        <v>-110</v>
       </c>
       <c r="E16">
-        <v>-145</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>4.27</v>
-      </c>
-      <c r="G16">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16">
-        <v>-0.23</v>
+        <v>45</v>
       </c>
       <c r="J16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K16">
-        <v>4.27</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="N16">
-        <v>824323</v>
+        <v>824163</v>
       </c>
       <c r="O16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P16">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2228,41 +2429,65 @@
       <c r="S16">
         <v>6</v>
       </c>
+      <c r="T16">
+        <v>0.2352</v>
+      </c>
+      <c r="U16">
+        <v>0.2422</v>
+      </c>
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>118</v>
+      </c>
+      <c r="X16">
+        <v>0.2542</v>
+      </c>
+      <c r="Y16">
+        <v>0.371</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
       <c r="AA16">
-        <v>4.55</v>
+        <v>4.15</v>
+      </c>
+      <c r="AB16">
+        <v>1.1645</v>
       </c>
       <c r="AC16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD16">
+        <v>0.2519</v>
+      </c>
+      <c r="AE16">
+        <v>0.2487</v>
+      </c>
+      <c r="AF16">
+        <v>9</v>
+      </c>
+      <c r="AG16">
+        <v>0.2197</v>
+      </c>
+      <c r="AH16">
+        <v>0.2163</v>
       </c>
       <c r="AI16">
-        <v>1.0205</v>
+        <v>1.111</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>3.73</v>
-      </c>
-      <c r="AO16">
-        <v>3.73</v>
-      </c>
-      <c r="AP16">
-        <v>3.73</v>
-      </c>
-      <c r="AQ16">
-        <v>3.73</v>
       </c>
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
@@ -2270,49 +2495,43 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C17">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="D17">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E17">
-        <v>-128</v>
+        <v>-121</v>
       </c>
       <c r="F17">
-        <v>8.49</v>
-      </c>
-      <c r="G17">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17">
-        <v>-1.01</v>
+        <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K17">
-        <v>9.87</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="M17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="N17">
-        <v>823996</v>
+        <v>824648</v>
       </c>
       <c r="O17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2323,41 +2542,65 @@
       <c r="S17">
         <v>6</v>
       </c>
+      <c r="T17">
+        <v>0.2644</v>
+      </c>
+      <c r="U17">
+        <v>0.2885</v>
+      </c>
+      <c r="V17">
+        <v>5</v>
+      </c>
+      <c r="W17">
+        <v>122</v>
+      </c>
+      <c r="X17">
+        <v>0.3279</v>
+      </c>
+      <c r="Y17">
+        <v>0.379</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
       <c r="AA17">
-        <v>3.8</v>
+        <v>4.08</v>
+      </c>
+      <c r="AB17">
+        <v>1.0189</v>
       </c>
       <c r="AC17" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD17">
+        <v>0.2204</v>
+      </c>
+      <c r="AE17">
+        <v>0.2218</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>0.218</v>
+      </c>
+      <c r="AH17">
+        <v>0.2163</v>
       </c>
       <c r="AI17">
-        <v>0.9443</v>
+        <v>0.9553</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM17">
-        <v>-1.38</v>
-      </c>
-      <c r="AN17">
-        <v>0.13</v>
-      </c>
-      <c r="AO17">
-        <v>0.13</v>
-      </c>
-      <c r="AP17">
-        <v>1.51</v>
-      </c>
-      <c r="AQ17">
-        <v>1.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
@@ -2365,49 +2608,112 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C18">
         <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-137</v>
+        <v>-143</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>124</v>
+      </c>
+      <c r="F18">
+        <v>5.91</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="K18">
+        <v>5.75</v>
       </c>
       <c r="L18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
-      </c>
-      <c r="N18" t="s">
-        <v>50</v>
+        <v>76</v>
+      </c>
+      <c r="N18">
+        <v>824648</v>
       </c>
       <c r="O18" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="P18">
+        <v>5.3</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
       </c>
       <c r="S18">
         <v>6</v>
       </c>
+      <c r="T18">
+        <v>0.1708</v>
+      </c>
+      <c r="U18">
+        <v>0.1788</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>114</v>
+      </c>
+      <c r="X18">
+        <v>0.193</v>
+      </c>
+      <c r="Y18">
+        <v>0.363</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>4.33</v>
+      </c>
+      <c r="AB18">
+        <v>1.3373</v>
+      </c>
       <c r="AC18" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD18">
+        <v>0.2893</v>
+      </c>
+      <c r="AE18">
+        <v>0.271</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>0.2439</v>
+      </c>
+      <c r="AH18">
+        <v>0.2163</v>
+      </c>
+      <c r="AI18">
+        <v>1.0471</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
       </c>
       <c r="AK18" t="s">
         <v>50</v>
       </c>
       <c r="AL18" t="s">
         <v>50</v>
+      </c>
+      <c r="AM18">
+        <v>0.16</v>
       </c>
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
@@ -2415,46 +2721,40 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E19">
-        <v>-132</v>
+        <v>-157</v>
       </c>
       <c r="F19">
-        <v>3.93</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
+        <v>3.84</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
       </c>
-      <c r="I19">
-        <v>0.43</v>
-      </c>
       <c r="J19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K19">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N19">
-        <v>824971</v>
+        <v>824323</v>
       </c>
       <c r="O19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P19">
         <v>5.6</v>
@@ -2468,41 +2768,65 @@
       <c r="S19">
         <v>6</v>
       </c>
+      <c r="T19">
+        <v>0.1818</v>
+      </c>
+      <c r="U19">
+        <v>0.1688</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
+      <c r="W19">
+        <v>122</v>
+      </c>
+      <c r="X19">
+        <v>0.1475</v>
+      </c>
+      <c r="Y19">
+        <v>0.379</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
       <c r="AA19">
-        <v>4.02</v>
+        <v>4.25</v>
+      </c>
+      <c r="AB19">
+        <v>0.9291</v>
       </c>
       <c r="AC19" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD19">
+        <v>0.201</v>
+      </c>
+      <c r="AE19">
+        <v>0.2071</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>0.2165</v>
+      </c>
+      <c r="AH19">
+        <v>0.2163</v>
       </c>
       <c r="AI19">
-        <v>0.9813</v>
+        <v>0.984</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>-1.93</v>
-      </c>
-      <c r="AO19">
-        <v>1.93</v>
-      </c>
-      <c r="AP19">
-        <v>-1.93</v>
-      </c>
-      <c r="AQ19">
-        <v>1.93</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
@@ -2510,49 +2834,43 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-108</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>-115</v>
+        <v>-145</v>
       </c>
       <c r="F20">
-        <v>5.24</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
       </c>
-      <c r="I20">
-        <v>-0.26</v>
-      </c>
       <c r="J20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K20">
-        <v>5.24</v>
+        <v>4.24</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N20">
-        <v>824971</v>
+        <v>824323</v>
       </c>
       <c r="O20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -2563,41 +2881,65 @@
       <c r="S20">
         <v>6</v>
       </c>
+      <c r="T20">
+        <v>0.1886</v>
+      </c>
+      <c r="U20">
+        <v>0.1925</v>
+      </c>
+      <c r="V20">
+        <v>5</v>
+      </c>
+      <c r="W20">
+        <v>131</v>
+      </c>
+      <c r="X20">
+        <v>0.1985</v>
+      </c>
+      <c r="Y20">
+        <v>0.396</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
       <c r="AA20">
-        <v>4.24</v>
+        <v>4.52</v>
+      </c>
+      <c r="AB20">
+        <v>0.8915</v>
       </c>
       <c r="AC20" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD20">
+        <v>0.1928</v>
+      </c>
+      <c r="AE20">
+        <v>0.216</v>
+      </c>
+      <c r="AF20">
+        <v>9</v>
+      </c>
+      <c r="AG20">
+        <v>0.2099</v>
+      </c>
+      <c r="AH20">
+        <v>0.2163</v>
       </c>
       <c r="AI20">
-        <v>0.917</v>
+        <v>1.0189</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>-0.24</v>
-      </c>
-      <c r="AO20">
-        <v>0.24</v>
-      </c>
-      <c r="AP20">
-        <v>-0.24</v>
-      </c>
-      <c r="AQ20">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
@@ -2605,46 +2947,40 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="D21">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>-113</v>
+        <v>-128</v>
       </c>
       <c r="F21">
-        <v>4.98</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
+        <v>9.65</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
       </c>
-      <c r="I21">
-        <v>-0.52</v>
-      </c>
       <c r="J21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K21">
-        <v>4.98</v>
+        <v>9.65</v>
       </c>
       <c r="L21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="N21">
-        <v>823107</v>
+        <v>823996</v>
       </c>
       <c r="O21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -2658,41 +2994,65 @@
       <c r="S21">
         <v>6</v>
       </c>
+      <c r="T21">
+        <v>0.4056</v>
+      </c>
+      <c r="U21">
+        <v>0.4219</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>106</v>
+      </c>
+      <c r="X21">
+        <v>0.4528</v>
+      </c>
+      <c r="Y21">
+        <v>0.346</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
       <c r="AA21">
-        <v>4.14</v>
+        <v>3.78</v>
+      </c>
+      <c r="AB21">
+        <v>1.0243</v>
       </c>
       <c r="AC21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD21">
+        <v>0.2216</v>
+      </c>
+      <c r="AE21">
+        <v>0.2312</v>
+      </c>
+      <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
+        <v>0.2505</v>
+      </c>
+      <c r="AH21">
+        <v>0.2163</v>
       </c>
       <c r="AI21">
-        <v>0.957</v>
+        <v>0.977</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM21">
         <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>-1.98</v>
-      </c>
-      <c r="AO21">
-        <v>1.98</v>
-      </c>
-      <c r="AP21">
-        <v>-1.98</v>
-      </c>
-      <c r="AQ21">
-        <v>1.98</v>
       </c>
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
@@ -2700,94 +3060,103 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22">
-        <v>6.5</v>
-      </c>
-      <c r="D22">
-        <v>-106</v>
-      </c>
-      <c r="E22">
-        <v>-105</v>
+        <v>83</v>
       </c>
       <c r="F22">
-        <v>6.77</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
+        <v>4.83</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
       </c>
-      <c r="I22">
-        <v>0.27</v>
-      </c>
       <c r="J22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K22">
-        <v>6.93</v>
+        <v>4.67</v>
       </c>
       <c r="L22" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="N22">
-        <v>823107</v>
+        <v>823996</v>
       </c>
       <c r="O22" t="s">
+        <v>48</v>
+      </c>
+      <c r="P22">
+        <v>5.3</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0.2225</v>
+      </c>
+      <c r="U22">
+        <v>0.2224</v>
+      </c>
+      <c r="V22">
+        <v>5</v>
+      </c>
+      <c r="W22">
+        <v>99</v>
+      </c>
+      <c r="X22">
+        <v>0.2222</v>
+      </c>
+      <c r="Y22">
+        <v>0.331</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>4.29</v>
+      </c>
+      <c r="AB22">
+        <v>0.9149</v>
+      </c>
+      <c r="AC22" t="s">
         <v>49</v>
       </c>
-      <c r="P22">
-        <v>5.7</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>6</v>
-      </c>
-      <c r="AA22">
-        <v>4.18</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>50</v>
+      <c r="AD22">
+        <v>0.1979</v>
+      </c>
+      <c r="AE22">
+        <v>0.2049</v>
+      </c>
+      <c r="AF22">
+        <v>9</v>
+      </c>
+      <c r="AG22">
+        <v>0.2141</v>
+      </c>
+      <c r="AH22">
+        <v>0.2163</v>
       </c>
       <c r="AI22">
-        <v>1.0114</v>
+        <v>1.0158</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM22">
-        <v>-0.16</v>
-      </c>
-      <c r="AN22">
-        <v>-4.93</v>
-      </c>
-      <c r="AO22">
-        <v>4.93</v>
-      </c>
-      <c r="AP22">
-        <v>-4.77</v>
-      </c>
-      <c r="AQ22">
-        <v>4.77</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
@@ -2795,49 +3164,43 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C23">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
-        <v>-137</v>
+        <v>124</v>
       </c>
       <c r="E23">
-        <v>120</v>
+        <v>-132</v>
       </c>
       <c r="F23">
-        <v>5.46</v>
-      </c>
-      <c r="G23">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23">
-        <v>0.96</v>
+        <v>45</v>
       </c>
       <c r="J23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K23">
-        <v>5.46</v>
+        <v>3.69</v>
       </c>
       <c r="L23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N23">
-        <v>823270</v>
+        <v>824971</v>
       </c>
       <c r="O23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P23">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -2848,41 +3211,65 @@
       <c r="S23">
         <v>6</v>
       </c>
+      <c r="T23">
+        <v>0.1748</v>
+      </c>
+      <c r="U23">
+        <v>0.1692</v>
+      </c>
+      <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>119</v>
+      </c>
+      <c r="X23">
+        <v>0.1597</v>
+      </c>
+      <c r="Y23">
+        <v>0.373</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
       <c r="AA23">
-        <v>4.18</v>
+        <v>4.02</v>
+      </c>
+      <c r="AB23">
+        <v>0.9619</v>
       </c>
       <c r="AC23" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="AD23">
+        <v>0.2081</v>
+      </c>
+      <c r="AE23">
+        <v>0.2113</v>
+      </c>
+      <c r="AF23">
+        <v>9</v>
+      </c>
+      <c r="AG23">
+        <v>0.2179</v>
+      </c>
+      <c r="AH23">
+        <v>0.2163</v>
       </c>
       <c r="AI23">
-        <v>0.9924</v>
+        <v>0.9925</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0.54</v>
-      </c>
-      <c r="AO23">
-        <v>0.54</v>
-      </c>
-      <c r="AP23">
-        <v>0.54</v>
-      </c>
-      <c r="AQ23">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
@@ -2890,94 +3277,112 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C24">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D24">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="E24">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F24">
-        <v>3.75</v>
-      </c>
-      <c r="G24">
-        <v>4</v>
+        <v>6.02</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
-      </c>
-      <c r="I24">
-        <v>0.25</v>
+        <v>45</v>
       </c>
       <c r="J24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K24">
-        <v>3.75</v>
+        <v>5.86</v>
       </c>
       <c r="L24" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N24">
-        <v>823919</v>
+        <v>824971</v>
       </c>
       <c r="O24" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24">
+        <v>5.2</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>6</v>
+      </c>
+      <c r="T24">
+        <v>0.2667</v>
+      </c>
+      <c r="U24">
+        <v>0.2872</v>
+      </c>
+      <c r="V24">
+        <v>5</v>
+      </c>
+      <c r="W24">
+        <v>111</v>
+      </c>
+      <c r="X24">
+        <v>0.3243</v>
+      </c>
+      <c r="Y24">
+        <v>0.357</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>4.33</v>
+      </c>
+      <c r="AB24">
+        <v>0.9996</v>
+      </c>
+      <c r="AC24" t="s">
         <v>49</v>
       </c>
-      <c r="P24">
-        <v>6</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>5</v>
-      </c>
-      <c r="AA24">
-        <v>3.9</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>50</v>
+      <c r="AD24">
+        <v>0.2162</v>
+      </c>
+      <c r="AE24">
+        <v>0.213</v>
+      </c>
+      <c r="AF24">
+        <v>9</v>
+      </c>
+      <c r="AG24">
+        <v>0.2263</v>
+      </c>
+      <c r="AH24">
+        <v>0.2163</v>
       </c>
       <c r="AI24">
-        <v>1.0041</v>
+        <v>0.9074</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="AL24" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>0.25</v>
-      </c>
-      <c r="AO24">
-        <v>0.25</v>
-      </c>
-      <c r="AP24">
-        <v>0.25</v>
-      </c>
-      <c r="AQ24">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
@@ -2985,94 +3390,112 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-130</v>
+        <v>-137</v>
       </c>
       <c r="E25">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F25">
-        <v>5.53</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
       </c>
-      <c r="I25">
-        <v>0.03</v>
-      </c>
       <c r="J25" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K25">
-        <v>5.53</v>
+        <v>4.39</v>
       </c>
       <c r="L25" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N25">
-        <v>823919</v>
+        <v>823270</v>
       </c>
       <c r="O25" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25">
+        <v>5.4</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>6</v>
+      </c>
+      <c r="T25">
+        <v>0.2356</v>
+      </c>
+      <c r="U25">
+        <v>0.2126</v>
+      </c>
+      <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>111</v>
+      </c>
+      <c r="X25">
+        <v>0.1712</v>
+      </c>
+      <c r="Y25">
+        <v>0.357</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>4.22</v>
+      </c>
+      <c r="AB25">
+        <v>0.9252</v>
+      </c>
+      <c r="AC25" t="s">
         <v>49</v>
       </c>
-      <c r="P25">
-        <v>4.9</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>5</v>
-      </c>
-      <c r="AA25">
-        <v>4.27</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>50</v>
+      <c r="AD25">
+        <v>0.2001</v>
+      </c>
+      <c r="AE25">
+        <v>0.2061</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>0.2198</v>
+      </c>
+      <c r="AH25">
+        <v>0.2163</v>
       </c>
       <c r="AI25">
-        <v>0.9909</v>
+        <v>0.9824</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>-1.53</v>
-      </c>
-      <c r="AO25">
-        <v>1.53</v>
-      </c>
-      <c r="AP25">
-        <v>-1.53</v>
-      </c>
-      <c r="AQ25">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
@@ -3080,67 +3503,103 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F26">
-        <v>5.6</v>
+        <v>1.81</v>
       </c>
       <c r="H26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>1.65</v>
       </c>
       <c r="L26" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M26" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="N26">
-        <v>824807</v>
+        <v>823270</v>
       </c>
       <c r="O26" t="s">
+        <v>90</v>
+      </c>
+      <c r="P26">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0.2199</v>
+      </c>
+      <c r="U26">
+        <v>0.2231</v>
+      </c>
+      <c r="V26">
+        <v>4</v>
+      </c>
+      <c r="W26">
+        <v>33</v>
+      </c>
+      <c r="X26">
+        <v>0.2424</v>
+      </c>
+      <c r="Y26">
+        <v>0.142</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>4.04</v>
+      </c>
+      <c r="AB26">
+        <v>0.9567</v>
+      </c>
+      <c r="AC26" t="s">
         <v>49</v>
       </c>
-      <c r="P26">
-        <v>5.4</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>4.23</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>50</v>
+      <c r="AD26">
+        <v>0.2069</v>
+      </c>
+      <c r="AE26">
+        <v>0.2152</v>
+      </c>
+      <c r="AF26">
+        <v>9</v>
+      </c>
+      <c r="AG26">
+        <v>0.2326</v>
+      </c>
+      <c r="AH26">
+        <v>0.2163</v>
       </c>
       <c r="AI26">
-        <v>0.989</v>
+        <v>0.8843</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
@@ -3148,67 +3607,112 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="C27">
+        <v>6.5</v>
+      </c>
+      <c r="D27">
+        <v>-106</v>
+      </c>
+      <c r="E27">
+        <v>-105</v>
       </c>
       <c r="F27">
-        <v>5.93</v>
+        <v>6.07</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K27">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="L27" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M27" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="N27">
-        <v>824404</v>
+        <v>823107</v>
       </c>
       <c r="O27" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27">
+        <v>5.7</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>6</v>
+      </c>
+      <c r="T27">
+        <v>0.2662</v>
+      </c>
+      <c r="U27">
+        <v>0.2561</v>
+      </c>
+      <c r="V27">
+        <v>5</v>
+      </c>
+      <c r="W27">
+        <v>125</v>
+      </c>
+      <c r="X27">
+        <v>0.24</v>
+      </c>
+      <c r="Y27">
+        <v>0.385</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>4.22</v>
+      </c>
+      <c r="AB27">
+        <v>0.9492</v>
+      </c>
+      <c r="AC27" t="s">
         <v>49</v>
       </c>
-      <c r="P27">
-        <v>5.9</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>3.98</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>50</v>
+      <c r="AD27">
+        <v>0.2053</v>
+      </c>
+      <c r="AE27">
+        <v>0.2072</v>
+      </c>
+      <c r="AF27">
+        <v>8</v>
+      </c>
+      <c r="AG27">
+        <v>0.2258</v>
+      </c>
+      <c r="AH27">
+        <v>0.2163</v>
       </c>
       <c r="AI27">
-        <v>0.88</v>
+        <v>1.0049</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
@@ -3216,67 +3720,112 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="C28">
+        <v>5.5</v>
+      </c>
+      <c r="D28">
+        <v>104</v>
+      </c>
+      <c r="E28">
+        <v>-113</v>
       </c>
       <c r="F28">
-        <v>4.72</v>
+        <v>4.39</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J28" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K28">
-        <v>4.72</v>
+        <v>4.23</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M28" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="N28">
-        <v>824483</v>
+        <v>823107</v>
       </c>
       <c r="O28" t="s">
+        <v>48</v>
+      </c>
+      <c r="P28">
+        <v>6</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>6</v>
+      </c>
+      <c r="T28">
+        <v>0.2063</v>
+      </c>
+      <c r="U28">
+        <v>0.2002</v>
+      </c>
+      <c r="V28">
+        <v>5</v>
+      </c>
+      <c r="W28">
+        <v>111</v>
+      </c>
+      <c r="X28">
+        <v>0.1892</v>
+      </c>
+      <c r="Y28">
+        <v>0.357</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>4.11</v>
+      </c>
+      <c r="AB28">
+        <v>0.9109</v>
+      </c>
+      <c r="AC28" t="s">
         <v>49</v>
       </c>
-      <c r="P28">
-        <v>5.2</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>4.31</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>50</v>
+      <c r="AD28">
+        <v>0.197</v>
+      </c>
+      <c r="AE28">
+        <v>0.2017</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>0.2106</v>
+      </c>
+      <c r="AH28">
+        <v>0.2163</v>
       </c>
       <c r="AI28">
-        <v>1.0345</v>
+        <v>0.9408</v>
       </c>
       <c r="AJ28" t="b">
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
@@ -3284,67 +3833,112 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="C29">
+        <v>3.5</v>
+      </c>
+      <c r="D29">
+        <v>-112</v>
+      </c>
+      <c r="E29">
+        <v>-105</v>
       </c>
       <c r="F29">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K29">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="L29" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M29" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="N29">
-        <v>822943</v>
+        <v>823919</v>
       </c>
       <c r="O29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P29">
+        <v>5.9</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>5</v>
+      </c>
+      <c r="T29">
+        <v>0.1803</v>
+      </c>
+      <c r="U29">
+        <v>0.1736</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>123</v>
+      </c>
+      <c r="X29">
+        <v>0.1626</v>
+      </c>
+      <c r="Y29">
+        <v>0.381</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>3.98</v>
+      </c>
+      <c r="AB29">
+        <v>0.8668</v>
+      </c>
+      <c r="AC29" t="s">
         <v>49</v>
       </c>
-      <c r="P29">
-        <v>4.8</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>4.49</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>50</v>
+      <c r="AD29">
+        <v>0.1875</v>
+      </c>
+      <c r="AE29">
+        <v>0.1949</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>0.1984</v>
+      </c>
+      <c r="AH29">
+        <v>0.2163</v>
       </c>
       <c r="AI29">
-        <v>0.88</v>
+        <v>0.9696</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
@@ -3352,67 +3946,112 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="C30">
+        <v>5.5</v>
+      </c>
+      <c r="D30">
+        <v>-130</v>
+      </c>
+      <c r="E30">
+        <v>115</v>
       </c>
       <c r="F30">
-        <v>4.89</v>
+        <v>5.55</v>
       </c>
       <c r="H30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K30">
-        <v>4.89</v>
+        <v>5.39</v>
       </c>
       <c r="L30" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M30" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="N30">
-        <v>823996</v>
+        <v>823919</v>
       </c>
       <c r="O30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30">
+        <v>4.8</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>5</v>
+      </c>
+      <c r="T30">
+        <v>0.2621</v>
+      </c>
+      <c r="U30">
+        <v>0.263</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>102</v>
+      </c>
+      <c r="X30">
+        <v>0.2647</v>
+      </c>
+      <c r="Y30">
+        <v>0.338</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>4.32</v>
+      </c>
+      <c r="AB30">
+        <v>0.9579</v>
+      </c>
+      <c r="AC30" t="s">
         <v>49</v>
       </c>
-      <c r="P30">
-        <v>5.4</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>4.3</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>50</v>
+      <c r="AD30">
+        <v>0.2072</v>
+      </c>
+      <c r="AE30">
+        <v>0.1983</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>0.2185</v>
+      </c>
+      <c r="AH30">
+        <v>0.2163</v>
       </c>
       <c r="AI30">
-        <v>1.0067</v>
+        <v>1.0388</v>
       </c>
       <c r="AJ30" t="b">
         <v>1</v>
       </c>
       <c r="AK30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AL30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
@@ -3420,67 +4059,49 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31">
-        <v>1.5</v>
+        <v>97</v>
+      </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>-137</v>
+      </c>
+      <c r="E31">
+        <v>120</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J31" t="s">
-        <v>50</v>
-      </c>
-      <c r="K31">
-        <v>1.5</v>
+        <v>45</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M31" t="s">
-        <v>90</v>
-      </c>
-      <c r="N31">
-        <v>823270</v>
+        <v>82</v>
+      </c>
+      <c r="N31" t="s">
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>101</v>
-      </c>
-      <c r="P31">
-        <v>1.9</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>4.11</v>
+        <v>6</v>
       </c>
       <c r="AC31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF31" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI31">
-        <v>0.8973</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="AK31" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AL31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
@@ -3488,7 +4109,7 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -3500,37 +4121,37 @@
         <v>-125</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M32" t="s">
         <v>70</v>
       </c>
       <c r="N32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S32">
         <v>1</v>
       </c>
       <c r="AC32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AK32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AL32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
@@ -3538,7 +4159,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C33">
         <v>5.5</v>
@@ -3553,25 +4174,25 @@
         <v>3.78</v>
       </c>
       <c r="H33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K33">
         <v>4.32</v>
       </c>
       <c r="L33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N33">
         <v>823270</v>
       </c>
       <c r="O33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P33">
         <v>5.7</v>
@@ -3589,10 +4210,10 @@
         <v>4.11</v>
       </c>
       <c r="AC33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AI33">
         <v>0.9483</v>
@@ -3601,10 +4222,10 @@
         <v>1</v>
       </c>
       <c r="AK33" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AL33" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
